--- a/Hlookup.xlsx
+++ b/Hlookup.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Data Analytics\ExcelSelfPractice\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Data Analytics\gitdata\practice25-repo\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F8BD427B-72A1-4843-8330-802EBAC2426E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A9452FE-63B8-4D6B-9785-920F1D6D79FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
   <metadataTypes count="1">
     <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
   </metadataTypes>
@@ -2572,6 +2572,10 @@
       <c r="F5" s="2">
         <v>165</v>
       </c>
+      <c r="H5">
+        <f>SUM(C2,D2)</f>
+        <v>550</v>
+      </c>
       <c r="M5">
         <f>IF(HLOOKUP(D1,B1:F21,MATCH("Router",B1:B21,0),FALSE)=" ","Data Missing",HLOOKUP(D1,B1:F21,MATCH("Router",B1:B21,0),FALSE))</f>
         <v>120</v>
